--- a/assingment/excel assingment/session - 13/SESSION -13.xlsx
+++ b/assingment/excel assingment/session - 13/SESSION -13.xlsx
@@ -1,27 +1,302 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\Tops\assingment\excel assingment\session - 13\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D19A119-092D-439E-869E-4F0F4246AD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="TASK - 2" sheetId="2" r:id="rId1"/>
+    <sheet name="TASK - 3" sheetId="3" r:id="rId2"/>
+    <sheet name="TASK -4" sheetId="4" r:id="rId3"/>
+    <sheet name="TASK - 1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="Slicer_City">#N/A</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="7" r:id="rId5"/>
+    <pivotCache cacheId="12" r:id="rId6"/>
+    <pivotCache cacheId="17" r:id="rId7"/>
+  </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId8"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="75">
+  <si>
+    <t>Order ID</t>
+  </si>
+  <si>
+    <t>Restaurant</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Delivery Partner</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>ORD001</t>
+  </si>
+  <si>
+    <t>Domino's</t>
+  </si>
+  <si>
+    <t>Ahmedabad</t>
+  </si>
+  <si>
+    <t>Zomato</t>
+  </si>
+  <si>
+    <t>ORD002</t>
+  </si>
+  <si>
+    <t>McDonald's</t>
+  </si>
+  <si>
+    <t>Surat</t>
+  </si>
+  <si>
+    <t>Swiggy</t>
+  </si>
+  <si>
+    <t>ORD003</t>
+  </si>
+  <si>
+    <t>KFC</t>
+  </si>
+  <si>
+    <t>Vadodara</t>
+  </si>
+  <si>
+    <t>ORD004</t>
+  </si>
+  <si>
+    <t>Pizza Hut</t>
+  </si>
+  <si>
+    <t>Rajkot</t>
+  </si>
+  <si>
+    <t>Blinkit</t>
+  </si>
+  <si>
+    <t>ORD005</t>
+  </si>
+  <si>
+    <t>Subway</t>
+  </si>
+  <si>
+    <t>ORD006</t>
+  </si>
+  <si>
+    <t>Burger King</t>
+  </si>
+  <si>
+    <t>ORD007</t>
+  </si>
+  <si>
+    <t>La Pino'z Pizza</t>
+  </si>
+  <si>
+    <t>ORD008</t>
+  </si>
+  <si>
+    <t>Taco Bell</t>
+  </si>
+  <si>
+    <t>ORD009</t>
+  </si>
+  <si>
+    <t>Hocco Eatery</t>
+  </si>
+  <si>
+    <t>ORD010</t>
+  </si>
+  <si>
+    <t>Honest</t>
+  </si>
+  <si>
+    <t>ORD011</t>
+  </si>
+  <si>
+    <t>ORD012</t>
+  </si>
+  <si>
+    <t>ORD013</t>
+  </si>
+  <si>
+    <t>ORD014</t>
+  </si>
+  <si>
+    <t>ORD015</t>
+  </si>
+  <si>
+    <t>ORD016</t>
+  </si>
+  <si>
+    <t>ORD017</t>
+  </si>
+  <si>
+    <t>ORD018</t>
+  </si>
+  <si>
+    <t>ORD019</t>
+  </si>
+  <si>
+    <t>ORD020</t>
+  </si>
+  <si>
+    <t>ORD021</t>
+  </si>
+  <si>
+    <t>ORD022</t>
+  </si>
+  <si>
+    <t>ORD023</t>
+  </si>
+  <si>
+    <t>ORD024</t>
+  </si>
+  <si>
+    <t>ORD025</t>
+  </si>
+  <si>
+    <t>ORD026</t>
+  </si>
+  <si>
+    <t>ORD027</t>
+  </si>
+  <si>
+    <t>ORD028</t>
+  </si>
+  <si>
+    <t>ORD029</t>
+  </si>
+  <si>
+    <t>ORD030</t>
+  </si>
+  <si>
+    <t>ORD031</t>
+  </si>
+  <si>
+    <t>ORD032</t>
+  </si>
+  <si>
+    <t>ORD033</t>
+  </si>
+  <si>
+    <t>ORD034</t>
+  </si>
+  <si>
+    <t>ORD035</t>
+  </si>
+  <si>
+    <t>ORD036</t>
+  </si>
+  <si>
+    <t>ORD037</t>
+  </si>
+  <si>
+    <t>ORD038</t>
+  </si>
+  <si>
+    <t>ORD039</t>
+  </si>
+  <si>
+    <t>ORD040</t>
+  </si>
+  <si>
+    <t>ORD041</t>
+  </si>
+  <si>
+    <t>ORD042</t>
+  </si>
+  <si>
+    <t>ORD043</t>
+  </si>
+  <si>
+    <t>ORD044</t>
+  </si>
+  <si>
+    <t>ORD045</t>
+  </si>
+  <si>
+    <t>ORD046</t>
+  </si>
+  <si>
+    <t>Bur</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Amount</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Count of Order ID</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -49,13 +324,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <numFmt numFmtId="168" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="35" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="35" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -66,6 +375,1516 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>586740</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>22861</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>327661</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="City">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FD2DED3-E699-BFA3-F532-62C817A466B1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="City"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6804660" y="388621"/>
+              <a:ext cx="1043940" cy="1767840"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="HP" refreshedDate="46226.762101388886" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="46" xr:uid="{E991EC56-7F74-4A7E-972A-B1CEEB80315B}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E47" sheet="TASK - 1"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Order ID" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Restaurant" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="City" numFmtId="0">
+      <sharedItems containsBlank="1" count="5">
+        <s v="Ahmedabad"/>
+        <s v="Surat"/>
+        <s v="Vadodara"/>
+        <s v="Rajkot"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Delivery Partner" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="270" maxValue="780"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="HP" refreshedDate="46226.763230902776" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="46" xr:uid="{764DC492-707F-41A7-8858-45EF5DFF225C}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E47" sheet="TASK - 2"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Order ID" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Restaurant" numFmtId="0">
+      <sharedItems count="11">
+        <s v="Domino's"/>
+        <s v="McDonald's"/>
+        <s v="KFC"/>
+        <s v="Pizza Hut"/>
+        <s v="Subway"/>
+        <s v="Burger King"/>
+        <s v="La Pino'z Pizza"/>
+        <s v="Taco Bell"/>
+        <s v="Hocco Eatery"/>
+        <s v="Honest"/>
+        <s v="Bur"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="City" numFmtId="0">
+      <sharedItems containsBlank="1" count="5">
+        <s v="Ahmedabad"/>
+        <s v="Surat"/>
+        <s v="Vadodara"/>
+        <s v="Rajkot"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Delivery Partner" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="270" maxValue="780"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="HP" refreshedDate="46226.764439120372" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="46" xr:uid="{BEFBE4E4-5FEE-4F90-A0C4-E0F32879BC9A}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E47" sheet="TASK - 3"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Order ID" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Restaurant" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="City" numFmtId="0">
+      <sharedItems containsBlank="1" count="5">
+        <s v="Ahmedabad"/>
+        <s v="Surat"/>
+        <s v="Vadodara"/>
+        <s v="Rajkot"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Delivery Partner" numFmtId="0">
+      <sharedItems containsBlank="1" count="4">
+        <s v="Zomato"/>
+        <s v="Swiggy"/>
+        <s v="Blinkit"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="270" maxValue="780"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="662199051"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="46">
+  <r>
+    <s v="ORD001"/>
+    <s v="Domino's"/>
+    <x v="0"/>
+    <s v="Zomato"/>
+    <n v="450"/>
+  </r>
+  <r>
+    <s v="ORD002"/>
+    <s v="McDonald's"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="320"/>
+  </r>
+  <r>
+    <s v="ORD003"/>
+    <s v="KFC"/>
+    <x v="2"/>
+    <s v="Zomato"/>
+    <n v="550"/>
+  </r>
+  <r>
+    <s v="ORD004"/>
+    <s v="Pizza Hut"/>
+    <x v="3"/>
+    <s v="Blinkit"/>
+    <n v="700"/>
+  </r>
+  <r>
+    <s v="ORD005"/>
+    <s v="Subway"/>
+    <x v="0"/>
+    <s v="Swiggy"/>
+    <n v="280"/>
+  </r>
+  <r>
+    <s v="ORD006"/>
+    <s v="Burger King"/>
+    <x v="1"/>
+    <s v="Zomato"/>
+    <n v="390"/>
+  </r>
+  <r>
+    <s v="ORD007"/>
+    <s v="La Pino'z Pizza"/>
+    <x v="0"/>
+    <s v="Swiggy"/>
+    <n v="610"/>
+  </r>
+  <r>
+    <s v="ORD008"/>
+    <s v="Taco Bell"/>
+    <x v="2"/>
+    <s v="Blinkit"/>
+    <n v="480"/>
+  </r>
+  <r>
+    <s v="ORD009"/>
+    <s v="Hocco Eatery"/>
+    <x v="3"/>
+    <s v="Zomato"/>
+    <n v="540"/>
+  </r>
+  <r>
+    <s v="ORD010"/>
+    <s v="Honest"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="360"/>
+  </r>
+  <r>
+    <s v="ORD011"/>
+    <s v="Domino's"/>
+    <x v="2"/>
+    <s v="Blinkit"/>
+    <n v="430"/>
+  </r>
+  <r>
+    <s v="ORD012"/>
+    <s v="McDonald's"/>
+    <x v="0"/>
+    <s v="Zomato"/>
+    <n v="510"/>
+  </r>
+  <r>
+    <s v="ORD013"/>
+    <s v="KFC"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="620"/>
+  </r>
+  <r>
+    <s v="ORD014"/>
+    <s v="Pizza Hut"/>
+    <x v="0"/>
+    <s v="Blinkit"/>
+    <n v="750"/>
+  </r>
+  <r>
+    <s v="ORD015"/>
+    <s v="Subway"/>
+    <x v="3"/>
+    <s v="Zomato"/>
+    <n v="290"/>
+  </r>
+  <r>
+    <s v="ORD016"/>
+    <s v="Burger King"/>
+    <x v="2"/>
+    <s v="Swiggy"/>
+    <n v="410"/>
+  </r>
+  <r>
+    <s v="ORD017"/>
+    <s v="La Pino'z Pizza"/>
+    <x v="1"/>
+    <s v="Blinkit"/>
+    <n v="680"/>
+  </r>
+  <r>
+    <s v="ORD018"/>
+    <s v="Taco Bell"/>
+    <x v="0"/>
+    <s v="Zomato"/>
+    <n v="460"/>
+  </r>
+  <r>
+    <s v="ORD019"/>
+    <s v="Hocco Eatery"/>
+    <x v="2"/>
+    <s v="Swiggy"/>
+    <n v="530"/>
+  </r>
+  <r>
+    <s v="ORD020"/>
+    <s v="Honest"/>
+    <x v="3"/>
+    <s v="Blinkit"/>
+    <n v="350"/>
+  </r>
+  <r>
+    <s v="ORD021"/>
+    <s v="Domino's"/>
+    <x v="1"/>
+    <s v="Zomato"/>
+    <n v="440"/>
+  </r>
+  <r>
+    <s v="ORD022"/>
+    <s v="McDonald's"/>
+    <x v="3"/>
+    <s v="Swiggy"/>
+    <n v="330"/>
+  </r>
+  <r>
+    <s v="ORD023"/>
+    <s v="KFC"/>
+    <x v="0"/>
+    <s v="Blinkit"/>
+    <n v="590"/>
+  </r>
+  <r>
+    <s v="ORD024"/>
+    <s v="Pizza Hut"/>
+    <x v="2"/>
+    <s v="Zomato"/>
+    <n v="720"/>
+  </r>
+  <r>
+    <s v="ORD025"/>
+    <s v="Subway"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="270"/>
+  </r>
+  <r>
+    <s v="ORD026"/>
+    <s v="Burger King"/>
+    <x v="0"/>
+    <s v="Blinkit"/>
+    <n v="420"/>
+  </r>
+  <r>
+    <s v="ORD027"/>
+    <s v="La Pino'z Pizza"/>
+    <x v="3"/>
+    <s v="Zomato"/>
+    <n v="650"/>
+  </r>
+  <r>
+    <s v="ORD028"/>
+    <s v="Taco Bell"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="470"/>
+  </r>
+  <r>
+    <s v="ORD029"/>
+    <s v="Hocco Eatery"/>
+    <x v="0"/>
+    <s v="Blinkit"/>
+    <n v="520"/>
+  </r>
+  <r>
+    <s v="ORD030"/>
+    <s v="Honest"/>
+    <x v="2"/>
+    <s v="Zomato"/>
+    <n v="340"/>
+  </r>
+  <r>
+    <s v="ORD031"/>
+    <s v="Domino's"/>
+    <x v="3"/>
+    <s v="Swiggy"/>
+    <n v="460"/>
+  </r>
+  <r>
+    <s v="ORD032"/>
+    <s v="McDonald's"/>
+    <x v="2"/>
+    <s v="Blinkit"/>
+    <n v="350"/>
+  </r>
+  <r>
+    <s v="ORD033"/>
+    <s v="KFC"/>
+    <x v="1"/>
+    <s v="Zomato"/>
+    <n v="610"/>
+  </r>
+  <r>
+    <s v="ORD034"/>
+    <s v="Pizza Hut"/>
+    <x v="0"/>
+    <s v="Swiggy"/>
+    <n v="780"/>
+  </r>
+  <r>
+    <s v="ORD035"/>
+    <s v="Subway"/>
+    <x v="2"/>
+    <s v="Blinkit"/>
+    <n v="300"/>
+  </r>
+  <r>
+    <s v="ORD036"/>
+    <s v="Burger King"/>
+    <x v="3"/>
+    <s v="Zomato"/>
+    <n v="430"/>
+  </r>
+  <r>
+    <s v="ORD037"/>
+    <s v="La Pino'z Pizza"/>
+    <x v="0"/>
+    <s v="Swiggy"/>
+    <n v="690"/>
+  </r>
+  <r>
+    <s v="ORD038"/>
+    <s v="Taco Bell"/>
+    <x v="2"/>
+    <s v="Blinkit"/>
+    <n v="490"/>
+  </r>
+  <r>
+    <s v="ORD039"/>
+    <s v="Hocco Eatery"/>
+    <x v="1"/>
+    <s v="Zomato"/>
+    <n v="550"/>
+  </r>
+  <r>
+    <s v="ORD040"/>
+    <s v="Honest"/>
+    <x v="0"/>
+    <s v="Swiggy"/>
+    <n v="370"/>
+  </r>
+  <r>
+    <s v="ORD041"/>
+    <s v="Domino's"/>
+    <x v="2"/>
+    <s v="Blinkit"/>
+    <n v="450"/>
+  </r>
+  <r>
+    <s v="ORD042"/>
+    <s v="McDonald's"/>
+    <x v="1"/>
+    <s v="Zomato"/>
+    <n v="340"/>
+  </r>
+  <r>
+    <s v="ORD043"/>
+    <s v="KFC"/>
+    <x v="3"/>
+    <s v="Swiggy"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <s v="ORD044"/>
+    <s v="Pizza Hut"/>
+    <x v="1"/>
+    <s v="Blinkit"/>
+    <n v="740"/>
+  </r>
+  <r>
+    <s v="ORD045"/>
+    <s v="Subway"/>
+    <x v="0"/>
+    <s v="Zomato"/>
+    <n v="310"/>
+  </r>
+  <r>
+    <s v="ORD046"/>
+    <s v="Bur"/>
+    <x v="4"/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="46">
+  <r>
+    <s v="ORD001"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Zomato"/>
+    <n v="450"/>
+  </r>
+  <r>
+    <s v="ORD002"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="320"/>
+  </r>
+  <r>
+    <s v="ORD003"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Zomato"/>
+    <n v="550"/>
+  </r>
+  <r>
+    <s v="ORD004"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Blinkit"/>
+    <n v="700"/>
+  </r>
+  <r>
+    <s v="ORD005"/>
+    <x v="4"/>
+    <x v="0"/>
+    <s v="Swiggy"/>
+    <n v="280"/>
+  </r>
+  <r>
+    <s v="ORD006"/>
+    <x v="5"/>
+    <x v="1"/>
+    <s v="Zomato"/>
+    <n v="390"/>
+  </r>
+  <r>
+    <s v="ORD007"/>
+    <x v="6"/>
+    <x v="0"/>
+    <s v="Swiggy"/>
+    <n v="610"/>
+  </r>
+  <r>
+    <s v="ORD008"/>
+    <x v="7"/>
+    <x v="2"/>
+    <s v="Blinkit"/>
+    <n v="480"/>
+  </r>
+  <r>
+    <s v="ORD009"/>
+    <x v="8"/>
+    <x v="3"/>
+    <s v="Zomato"/>
+    <n v="540"/>
+  </r>
+  <r>
+    <s v="ORD010"/>
+    <x v="9"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="360"/>
+  </r>
+  <r>
+    <s v="ORD011"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Blinkit"/>
+    <n v="430"/>
+  </r>
+  <r>
+    <s v="ORD012"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Zomato"/>
+    <n v="510"/>
+  </r>
+  <r>
+    <s v="ORD013"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="620"/>
+  </r>
+  <r>
+    <s v="ORD014"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Blinkit"/>
+    <n v="750"/>
+  </r>
+  <r>
+    <s v="ORD015"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="Zomato"/>
+    <n v="290"/>
+  </r>
+  <r>
+    <s v="ORD016"/>
+    <x v="5"/>
+    <x v="2"/>
+    <s v="Swiggy"/>
+    <n v="410"/>
+  </r>
+  <r>
+    <s v="ORD017"/>
+    <x v="6"/>
+    <x v="1"/>
+    <s v="Blinkit"/>
+    <n v="680"/>
+  </r>
+  <r>
+    <s v="ORD018"/>
+    <x v="7"/>
+    <x v="0"/>
+    <s v="Zomato"/>
+    <n v="460"/>
+  </r>
+  <r>
+    <s v="ORD019"/>
+    <x v="8"/>
+    <x v="2"/>
+    <s v="Swiggy"/>
+    <n v="530"/>
+  </r>
+  <r>
+    <s v="ORD020"/>
+    <x v="9"/>
+    <x v="3"/>
+    <s v="Blinkit"/>
+    <n v="350"/>
+  </r>
+  <r>
+    <s v="ORD021"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Zomato"/>
+    <n v="440"/>
+  </r>
+  <r>
+    <s v="ORD022"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Swiggy"/>
+    <n v="330"/>
+  </r>
+  <r>
+    <s v="ORD023"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Blinkit"/>
+    <n v="590"/>
+  </r>
+  <r>
+    <s v="ORD024"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Zomato"/>
+    <n v="720"/>
+  </r>
+  <r>
+    <s v="ORD025"/>
+    <x v="4"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="270"/>
+  </r>
+  <r>
+    <s v="ORD026"/>
+    <x v="5"/>
+    <x v="0"/>
+    <s v="Blinkit"/>
+    <n v="420"/>
+  </r>
+  <r>
+    <s v="ORD027"/>
+    <x v="6"/>
+    <x v="3"/>
+    <s v="Zomato"/>
+    <n v="650"/>
+  </r>
+  <r>
+    <s v="ORD028"/>
+    <x v="7"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="470"/>
+  </r>
+  <r>
+    <s v="ORD029"/>
+    <x v="8"/>
+    <x v="0"/>
+    <s v="Blinkit"/>
+    <n v="520"/>
+  </r>
+  <r>
+    <s v="ORD030"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="Zomato"/>
+    <n v="340"/>
+  </r>
+  <r>
+    <s v="ORD031"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Swiggy"/>
+    <n v="460"/>
+  </r>
+  <r>
+    <s v="ORD032"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Blinkit"/>
+    <n v="350"/>
+  </r>
+  <r>
+    <s v="ORD033"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Zomato"/>
+    <n v="610"/>
+  </r>
+  <r>
+    <s v="ORD034"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Swiggy"/>
+    <n v="780"/>
+  </r>
+  <r>
+    <s v="ORD035"/>
+    <x v="4"/>
+    <x v="2"/>
+    <s v="Blinkit"/>
+    <n v="300"/>
+  </r>
+  <r>
+    <s v="ORD036"/>
+    <x v="5"/>
+    <x v="3"/>
+    <s v="Zomato"/>
+    <n v="430"/>
+  </r>
+  <r>
+    <s v="ORD037"/>
+    <x v="6"/>
+    <x v="0"/>
+    <s v="Swiggy"/>
+    <n v="690"/>
+  </r>
+  <r>
+    <s v="ORD038"/>
+    <x v="7"/>
+    <x v="2"/>
+    <s v="Blinkit"/>
+    <n v="490"/>
+  </r>
+  <r>
+    <s v="ORD039"/>
+    <x v="8"/>
+    <x v="1"/>
+    <s v="Zomato"/>
+    <n v="550"/>
+  </r>
+  <r>
+    <s v="ORD040"/>
+    <x v="9"/>
+    <x v="0"/>
+    <s v="Swiggy"/>
+    <n v="370"/>
+  </r>
+  <r>
+    <s v="ORD041"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Blinkit"/>
+    <n v="450"/>
+  </r>
+  <r>
+    <s v="ORD042"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Zomato"/>
+    <n v="340"/>
+  </r>
+  <r>
+    <s v="ORD043"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Swiggy"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <s v="ORD044"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Blinkit"/>
+    <n v="740"/>
+  </r>
+  <r>
+    <s v="ORD045"/>
+    <x v="4"/>
+    <x v="0"/>
+    <s v="Zomato"/>
+    <n v="310"/>
+  </r>
+  <r>
+    <s v="ORD046"/>
+    <x v="10"/>
+    <x v="4"/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="46">
+  <r>
+    <s v="ORD001"/>
+    <s v="Domino's"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="450"/>
+  </r>
+  <r>
+    <s v="ORD002"/>
+    <s v="McDonald's"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="320"/>
+  </r>
+  <r>
+    <s v="ORD003"/>
+    <s v="KFC"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="550"/>
+  </r>
+  <r>
+    <s v="ORD004"/>
+    <s v="Pizza Hut"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="700"/>
+  </r>
+  <r>
+    <s v="ORD005"/>
+    <s v="Subway"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="280"/>
+  </r>
+  <r>
+    <s v="ORD006"/>
+    <s v="Burger King"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="390"/>
+  </r>
+  <r>
+    <s v="ORD007"/>
+    <s v="La Pino'z Pizza"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="610"/>
+  </r>
+  <r>
+    <s v="ORD008"/>
+    <s v="Taco Bell"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="480"/>
+  </r>
+  <r>
+    <s v="ORD009"/>
+    <s v="Hocco Eatery"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="540"/>
+  </r>
+  <r>
+    <s v="ORD010"/>
+    <s v="Honest"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="360"/>
+  </r>
+  <r>
+    <s v="ORD011"/>
+    <s v="Domino's"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="430"/>
+  </r>
+  <r>
+    <s v="ORD012"/>
+    <s v="McDonald's"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="510"/>
+  </r>
+  <r>
+    <s v="ORD013"/>
+    <s v="KFC"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="620"/>
+  </r>
+  <r>
+    <s v="ORD014"/>
+    <s v="Pizza Hut"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="750"/>
+  </r>
+  <r>
+    <s v="ORD015"/>
+    <s v="Subway"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="290"/>
+  </r>
+  <r>
+    <s v="ORD016"/>
+    <s v="Burger King"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="410"/>
+  </r>
+  <r>
+    <s v="ORD017"/>
+    <s v="La Pino'z Pizza"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="680"/>
+  </r>
+  <r>
+    <s v="ORD018"/>
+    <s v="Taco Bell"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="460"/>
+  </r>
+  <r>
+    <s v="ORD019"/>
+    <s v="Hocco Eatery"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="530"/>
+  </r>
+  <r>
+    <s v="ORD020"/>
+    <s v="Honest"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="350"/>
+  </r>
+  <r>
+    <s v="ORD021"/>
+    <s v="Domino's"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="440"/>
+  </r>
+  <r>
+    <s v="ORD022"/>
+    <s v="McDonald's"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="330"/>
+  </r>
+  <r>
+    <s v="ORD023"/>
+    <s v="KFC"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="590"/>
+  </r>
+  <r>
+    <s v="ORD024"/>
+    <s v="Pizza Hut"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="720"/>
+  </r>
+  <r>
+    <s v="ORD025"/>
+    <s v="Subway"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="270"/>
+  </r>
+  <r>
+    <s v="ORD026"/>
+    <s v="Burger King"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="420"/>
+  </r>
+  <r>
+    <s v="ORD027"/>
+    <s v="La Pino'z Pizza"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="650"/>
+  </r>
+  <r>
+    <s v="ORD028"/>
+    <s v="Taco Bell"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="470"/>
+  </r>
+  <r>
+    <s v="ORD029"/>
+    <s v="Hocco Eatery"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="520"/>
+  </r>
+  <r>
+    <s v="ORD030"/>
+    <s v="Honest"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="340"/>
+  </r>
+  <r>
+    <s v="ORD031"/>
+    <s v="Domino's"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="460"/>
+  </r>
+  <r>
+    <s v="ORD032"/>
+    <s v="McDonald's"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="350"/>
+  </r>
+  <r>
+    <s v="ORD033"/>
+    <s v="KFC"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="610"/>
+  </r>
+  <r>
+    <s v="ORD034"/>
+    <s v="Pizza Hut"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="780"/>
+  </r>
+  <r>
+    <s v="ORD035"/>
+    <s v="Subway"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="300"/>
+  </r>
+  <r>
+    <s v="ORD036"/>
+    <s v="Burger King"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="430"/>
+  </r>
+  <r>
+    <s v="ORD037"/>
+    <s v="La Pino'z Pizza"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="690"/>
+  </r>
+  <r>
+    <s v="ORD038"/>
+    <s v="Taco Bell"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="490"/>
+  </r>
+  <r>
+    <s v="ORD039"/>
+    <s v="Hocco Eatery"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="550"/>
+  </r>
+  <r>
+    <s v="ORD040"/>
+    <s v="Honest"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="370"/>
+  </r>
+  <r>
+    <s v="ORD041"/>
+    <s v="Domino's"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="450"/>
+  </r>
+  <r>
+    <s v="ORD042"/>
+    <s v="McDonald's"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="340"/>
+  </r>
+  <r>
+    <s v="ORD043"/>
+    <s v="KFC"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <s v="ORD044"/>
+    <s v="Pizza Hut"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="740"/>
+  </r>
+  <r>
+    <s v="ORD045"/>
+    <s v="Subway"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="310"/>
+  </r>
+  <r>
+    <s v="ORD046"/>
+    <s v="Bur"/>
+    <x v="4"/>
+    <x v="3"/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{59C3019B-562A-4844-99D1-F99269688ECE}" name="PivotTable3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="I4:O17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="12">
+        <item x="10"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C65F5E46-83D5-4CAF-91D0-41E943A37665}" name="PivotTable4" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H2:I7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="3" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F19ED798-5CD4-44B0-8725-003DD1CE68B3}" name="PivotTable5" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H2:I6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="3" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6990207D-B2B5-435F-B707-1027BEA66544}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H2:I8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="4" baseField="0" baseItem="0" numFmtId="169"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="1">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_City" xr10:uid="{E40E27FF-AFEE-4262-9BF5-2199C9AE55C3}" sourceName="City">
+  <pivotTables>
+    <pivotTable tabId="4" name="PivotTable5"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="662199051">
+      <items count="5">
+        <i x="0" s="1"/>
+        <i x="3"/>
+        <i x="1"/>
+        <i x="2"/>
+        <i x="4"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="City" xr10:uid="{123F1D71-FEBC-4BBF-A1C4-4A5A0B31BFDC}" cache="Slicer_City" caption="City" rowHeight="234950"/>
+</slicers>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +2149,3589 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEEADDA8-758D-4326-BB35-177C018276E7}">
+  <dimension ref="A1:O47"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3">
+        <v>550</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3">
+        <v>700</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" t="s">
+        <v>70</v>
+      </c>
+      <c r="O5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3">
+        <v>280</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+    </row>
+    <row r="7" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="3">
+        <v>390</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="7">
+        <v>420</v>
+      </c>
+      <c r="K7" s="7">
+        <v>430</v>
+      </c>
+      <c r="L7" s="7">
+        <v>390</v>
+      </c>
+      <c r="M7" s="7">
+        <v>410</v>
+      </c>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="3">
+        <v>610</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" s="7">
+        <v>450</v>
+      </c>
+      <c r="K8" s="7">
+        <v>460</v>
+      </c>
+      <c r="L8" s="7">
+        <v>440</v>
+      </c>
+      <c r="M8" s="7">
+        <v>880</v>
+      </c>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="3">
+        <v>480</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="7">
+        <v>520</v>
+      </c>
+      <c r="K9" s="7">
+        <v>540</v>
+      </c>
+      <c r="L9" s="7">
+        <v>550</v>
+      </c>
+      <c r="M9" s="7">
+        <v>530</v>
+      </c>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>540</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="7">
+        <v>370</v>
+      </c>
+      <c r="K10" s="7">
+        <v>350</v>
+      </c>
+      <c r="L10" s="7">
+        <v>360</v>
+      </c>
+      <c r="M10" s="7">
+        <v>340</v>
+      </c>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="3">
+        <v>360</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7">
+        <v>590</v>
+      </c>
+      <c r="K11" s="7">
+        <v>600</v>
+      </c>
+      <c r="L11" s="7">
+        <v>1230</v>
+      </c>
+      <c r="M11" s="7">
+        <v>550</v>
+      </c>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="3">
+        <v>430</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" s="7">
+        <v>1300</v>
+      </c>
+      <c r="K12" s="7">
+        <v>650</v>
+      </c>
+      <c r="L12" s="7">
+        <v>680</v>
+      </c>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="3">
+        <v>510</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="7">
+        <v>510</v>
+      </c>
+      <c r="K13" s="7">
+        <v>330</v>
+      </c>
+      <c r="L13" s="7">
+        <v>660</v>
+      </c>
+      <c r="M13" s="7">
+        <v>350</v>
+      </c>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="3">
+        <v>620</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="7">
+        <v>1530</v>
+      </c>
+      <c r="K14" s="7">
+        <v>700</v>
+      </c>
+      <c r="L14" s="7">
+        <v>740</v>
+      </c>
+      <c r="M14" s="7">
+        <v>720</v>
+      </c>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7">
+        <v>3690</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="3">
+        <v>750</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="7">
+        <v>590</v>
+      </c>
+      <c r="K15" s="7">
+        <v>290</v>
+      </c>
+      <c r="L15" s="7">
+        <v>270</v>
+      </c>
+      <c r="M15" s="7">
+        <v>300</v>
+      </c>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3">
+        <v>290</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="7">
+        <v>460</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7">
+        <v>470</v>
+      </c>
+      <c r="M16" s="7">
+        <v>970</v>
+      </c>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="3">
+        <v>410</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17" s="7">
+        <v>6740</v>
+      </c>
+      <c r="K17" s="7">
+        <v>4350</v>
+      </c>
+      <c r="L17" s="7">
+        <v>5790</v>
+      </c>
+      <c r="M17" s="7">
+        <v>5050</v>
+      </c>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7">
+        <v>21930</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="3">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="3">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="3">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="3">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="3">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="3">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="3">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="3">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{473E6222-417A-406F-8CB2-8B34896ACE96}">
+  <dimension ref="A1:I47"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3">
+        <v>450</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3">
+        <v>320</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3">
+        <v>550</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3">
+        <v>700</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3">
+        <v>280</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="3">
+        <v>390</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" s="7">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="3">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="3">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="3">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="3">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="3">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="3">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="3">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="3">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="3">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="3">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="3">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252BB278-3C06-4194-8515-9E84E279E722}">
+  <dimension ref="A1:I47"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3">
+        <v>450</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3">
+        <v>320</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3">
+        <v>550</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3">
+        <v>700</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3">
+        <v>280</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="3">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="3">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="3">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="3">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="3">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="3">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="3">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="3">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="3">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="3">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="3">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="3">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I47"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3">
+        <v>450</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3">
+        <v>320</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="8">
+        <v>6740</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3">
+        <v>550</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="8">
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3">
+        <v>700</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="8">
+        <v>5790</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3">
+        <v>280</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="8">
+        <v>5050</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="3">
+        <v>390</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="8"/>
+    </row>
+    <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="3">
+        <v>610</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" s="8">
+        <v>21930</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="3">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="3">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="3">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="3">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="3">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="3">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="3">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="3">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="3">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="3">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="3">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="3"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>